--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/40.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/40.xlsx
@@ -426,13 +426,13 @@
         <v>-13.14005992228332</v>
       </c>
       <c r="E2">
-        <v>-4.026080054504437</v>
+        <v>-6.493369999822678</v>
       </c>
       <c r="F2">
-        <v>2.633190130116879</v>
+        <v>3.246536549436912</v>
       </c>
       <c r="G2">
-        <v>-16.56523915505949</v>
+        <v>-18.96502252948787</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.20246259947343</v>
       </c>
       <c r="E3">
-        <v>-4.938274777044478</v>
+        <v>-6.3190555673083</v>
       </c>
       <c r="F3">
-        <v>2.851332401970101</v>
+        <v>3.098371442302581</v>
       </c>
       <c r="G3">
-        <v>-16.34070598261768</v>
+        <v>-18.6438539513783</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.0297671104231</v>
       </c>
       <c r="E4">
-        <v>-6.1331287559297</v>
+        <v>-7.733132652763272</v>
       </c>
       <c r="F4">
-        <v>2.968181907808999</v>
+        <v>3.152712343926229</v>
       </c>
       <c r="G4">
-        <v>-15.5885348014504</v>
+        <v>-17.9715663332099</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.77335442397807</v>
       </c>
       <c r="E5">
-        <v>-6.127127365565324</v>
+        <v>-7.698964183193908</v>
       </c>
       <c r="F5">
-        <v>3.062559462744753</v>
+        <v>3.4064064879728</v>
       </c>
       <c r="G5">
-        <v>-14.82082446847681</v>
+        <v>-17.26429995900976</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.470142883096997</v>
       </c>
       <c r="E6">
-        <v>-9.229032154528692</v>
+        <v>-8.859201145686685</v>
       </c>
       <c r="F6">
-        <v>3.187821867926483</v>
+        <v>3.651828555135015</v>
       </c>
       <c r="G6">
-        <v>-13.89654778237415</v>
+        <v>-16.5100649842432</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.207419667248132</v>
       </c>
       <c r="E7">
-        <v>-9.232911253906082</v>
+        <v>-9.044164412037924</v>
       </c>
       <c r="F7">
-        <v>3.251511724058126</v>
+        <v>3.444163474192401</v>
       </c>
       <c r="G7">
-        <v>-13.5399735914922</v>
+        <v>-16.2123487247956</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.021271353935468</v>
       </c>
       <c r="E8">
-        <v>-9.763816257558913</v>
+        <v>-10.13538746194602</v>
       </c>
       <c r="F8">
-        <v>3.060682382210009</v>
+        <v>4.009839006216128</v>
       </c>
       <c r="G8">
-        <v>-12.85408007788721</v>
+        <v>-15.63403485818432</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.959048700045586</v>
       </c>
       <c r="E9">
-        <v>-9.166904266320582</v>
+        <v>-10.13671648956997</v>
       </c>
       <c r="F9">
-        <v>3.487810152645907</v>
+        <v>4.087137282040961</v>
       </c>
       <c r="G9">
-        <v>-13.01609244423334</v>
+        <v>-14.40475271373567</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.031038792579362</v>
       </c>
       <c r="E10">
-        <v>-10.18875622747007</v>
+        <v>-11.43815848389559</v>
       </c>
       <c r="F10">
-        <v>4.119940631191821</v>
+        <v>4.00674753906888</v>
       </c>
       <c r="G10">
-        <v>-11.88540376389579</v>
+        <v>-14.08443132224592</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.232005178493739</v>
       </c>
       <c r="E11">
-        <v>-10.3097683458416</v>
+        <v>-11.53106582123201</v>
       </c>
       <c r="F11">
-        <v>4.262391659981641</v>
+        <v>4.267257490105685</v>
       </c>
       <c r="G11">
-        <v>-11.32685453921153</v>
+        <v>-13.3963134542493</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.546770083444128</v>
       </c>
       <c r="E12">
-        <v>-11.29180347001996</v>
+        <v>-12.3493107503931</v>
       </c>
       <c r="F12">
-        <v>4.09038613899474</v>
+        <v>4.666412950083849</v>
       </c>
       <c r="G12">
-        <v>-10.97874699303856</v>
+        <v>-12.39864090545668</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.938260531989626</v>
       </c>
       <c r="E13">
-        <v>-12.37446675138759</v>
+        <v>-13.04172998925719</v>
       </c>
       <c r="F13">
-        <v>4.552118129315184</v>
+        <v>4.758578764054127</v>
       </c>
       <c r="G13">
-        <v>-10.52687540309178</v>
+        <v>-11.8642475951017</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.378693688231246</v>
       </c>
       <c r="E14">
-        <v>-13.7549111315341</v>
+        <v>-14.32342761694458</v>
       </c>
       <c r="F14">
-        <v>4.676232417276634</v>
+        <v>4.921021611743111</v>
       </c>
       <c r="G14">
-        <v>-9.075669525420141</v>
+        <v>-11.10302235169243</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.836137512474855</v>
       </c>
       <c r="E15">
-        <v>-13.7138275651089</v>
+        <v>-14.57075135133812</v>
       </c>
       <c r="F15">
-        <v>4.645995350339647</v>
+        <v>4.956995951311888</v>
       </c>
       <c r="G15">
-        <v>-9.115966368183976</v>
+        <v>-11.11123314343149</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.2811777382210155</v>
       </c>
       <c r="E16">
-        <v>-15.37611717218092</v>
+        <v>-15.96425758110122</v>
       </c>
       <c r="F16">
-        <v>4.812132716645116</v>
+        <v>5.426415191130312</v>
       </c>
       <c r="G16">
-        <v>-8.285005526001482</v>
+        <v>-9.811124108970528</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.2996730215469935</v>
       </c>
       <c r="E17">
-        <v>-15.51435681112784</v>
+        <v>-16.92144404192312</v>
       </c>
       <c r="F17">
-        <v>5.646200943910688</v>
+        <v>5.542078474848401</v>
       </c>
       <c r="G17">
-        <v>-8.177377580232838</v>
+        <v>-9.227903347900252</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.9186961923285965</v>
       </c>
       <c r="E18">
-        <v>-16.93919902033677</v>
+        <v>-17.18858690075875</v>
       </c>
       <c r="F18">
-        <v>5.094644105900276</v>
+        <v>5.66605028361657</v>
       </c>
       <c r="G18">
-        <v>-7.270438848959767</v>
+        <v>-8.906965820686992</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.570290082893197</v>
       </c>
       <c r="E19">
-        <v>-18.30485796816689</v>
+        <v>-18.14329804763106</v>
       </c>
       <c r="F19">
-        <v>5.796652345076745</v>
+        <v>5.747452291554871</v>
       </c>
       <c r="G19">
-        <v>-6.831220232673823</v>
+        <v>-8.158030657440392</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.239258847726616</v>
       </c>
       <c r="E20">
-        <v>-16.70553935120191</v>
+        <v>-19.31742750200538</v>
       </c>
       <c r="F20">
-        <v>5.768857305243211</v>
+        <v>6.092831796478097</v>
       </c>
       <c r="G20">
-        <v>-7.021138847954359</v>
+        <v>-7.847523054868629</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.906554052744329</v>
       </c>
       <c r="E21">
-        <v>-19.33279023069592</v>
+        <v>-19.42749175532467</v>
       </c>
       <c r="F21">
-        <v>5.778585652021688</v>
+        <v>5.926888268144883</v>
       </c>
       <c r="G21">
-        <v>-6.765137065583564</v>
+        <v>-7.176556473463333</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.54239432353465</v>
       </c>
       <c r="E22">
-        <v>-18.4649601115277</v>
+        <v>-20.0249395108239</v>
       </c>
       <c r="F22">
-        <v>5.979032339416307</v>
+        <v>5.793378637100881</v>
       </c>
       <c r="G22">
-        <v>-6.37579933545543</v>
+        <v>-7.132045888929443</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.122141655525978</v>
       </c>
       <c r="E23">
-        <v>-19.51824357598349</v>
+        <v>-19.89473633579053</v>
       </c>
       <c r="F23">
-        <v>6.01019717784443</v>
+        <v>5.680612982557784</v>
       </c>
       <c r="G23">
-        <v>-6.084032962930974</v>
+        <v>-6.597561202513775</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.623889854529684</v>
       </c>
       <c r="E24">
-        <v>-20.45319374337227</v>
+        <v>-20.57575916277928</v>
       </c>
       <c r="F24">
-        <v>6.31204266228093</v>
+        <v>5.624030518742162</v>
       </c>
       <c r="G24">
-        <v>-5.555542546096503</v>
+        <v>-6.435961333813045</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>5.031425737019129</v>
       </c>
       <c r="E25">
-        <v>-20.09838905310349</v>
+        <v>-20.65820456078846</v>
       </c>
       <c r="F25">
-        <v>5.676930061084938</v>
+        <v>5.628270103109689</v>
       </c>
       <c r="G25">
-        <v>-5.365597823370056</v>
+        <v>-6.275828703572521</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>5.344215893049672</v>
       </c>
       <c r="E26">
-        <v>-18.79148973909705</v>
+        <v>-21.48359301342826</v>
       </c>
       <c r="F26">
-        <v>6.072533481639898</v>
+        <v>5.43679463468739</v>
       </c>
       <c r="G26">
-        <v>-5.575138794997399</v>
+        <v>-5.8506167320179</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.565042982664591</v>
       </c>
       <c r="E27">
-        <v>-20.35670633787386</v>
+        <v>-21.52250445033058</v>
       </c>
       <c r="F27">
-        <v>5.722269922509766</v>
+        <v>5.322344080846999</v>
       </c>
       <c r="G27">
-        <v>-5.460829953820095</v>
+        <v>-5.696397438276247</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.708111135549023</v>
       </c>
       <c r="E28">
-        <v>-19.00431274701523</v>
+        <v>-21.69978842894221</v>
       </c>
       <c r="F28">
-        <v>5.980256666437644</v>
+        <v>5.238809855213891</v>
       </c>
       <c r="G28">
-        <v>-5.703725798343502</v>
+        <v>-5.571287946725507</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.793412933040625</v>
       </c>
       <c r="E29">
-        <v>-21.28084984939543</v>
+        <v>-20.83456237327465</v>
       </c>
       <c r="F29">
-        <v>5.867921762944003</v>
+        <v>5.176586209385203</v>
       </c>
       <c r="G29">
-        <v>-5.421590462615662</v>
+        <v>-5.885579823582089</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.838519824025658</v>
       </c>
       <c r="E30">
-        <v>-21.09475690956383</v>
+        <v>-21.60390323908589</v>
       </c>
       <c r="F30">
-        <v>6.116226548667961</v>
+        <v>5.153499609869181</v>
       </c>
       <c r="G30">
-        <v>-5.586941971293823</v>
+        <v>-5.787086873137749</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.866427944343694</v>
       </c>
       <c r="E31">
-        <v>-19.52119235602412</v>
+        <v>-21.74365464695505</v>
       </c>
       <c r="F31">
-        <v>5.694194894494085</v>
+        <v>5.276397854483321</v>
       </c>
       <c r="G31">
-        <v>-5.629502329618151</v>
+        <v>-6.095674273062748</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.889524468517568</v>
       </c>
       <c r="E32">
-        <v>-19.96899160106713</v>
+        <v>-20.33171646533236</v>
       </c>
       <c r="F32">
-        <v>5.572698247525482</v>
+        <v>5.234537136150251</v>
       </c>
       <c r="G32">
-        <v>-5.233637738012234</v>
+        <v>-5.988685959718926</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.916230121309846</v>
       </c>
       <c r="E33">
-        <v>-19.66074856296101</v>
+        <v>-20.82973218850388</v>
       </c>
       <c r="F33">
-        <v>5.406920392672828</v>
+        <v>5.264981294937939</v>
       </c>
       <c r="G33">
-        <v>-6.609202512645549</v>
+        <v>-6.650146820067979</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.95061186061367</v>
       </c>
       <c r="E34">
-        <v>-18.55270916039868</v>
+        <v>-20.69503523881704</v>
       </c>
       <c r="F34">
-        <v>5.801332620902563</v>
+        <v>5.471509855803911</v>
       </c>
       <c r="G34">
-        <v>-6.133929513556331</v>
+        <v>-6.51807447269274</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.985146202160891</v>
       </c>
       <c r="E35">
-        <v>-18.6054881699146</v>
+        <v>-19.86765739795264</v>
       </c>
       <c r="F35">
-        <v>5.722977348271757</v>
+        <v>5.723293784619626</v>
       </c>
       <c r="G35">
-        <v>-6.596420307127459</v>
+        <v>-6.947351373575724</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>6.015860049868991</v>
       </c>
       <c r="E36">
-        <v>-17.54452126450787</v>
+        <v>-19.49161318496869</v>
       </c>
       <c r="F36">
-        <v>5.580542886829993</v>
+        <v>5.590204964216246</v>
       </c>
       <c r="G36">
-        <v>-6.744034417053595</v>
+        <v>-6.999944823363702</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>6.029627862475396</v>
       </c>
       <c r="E37">
-        <v>-17.76438811883297</v>
+        <v>-19.40634775646996</v>
       </c>
       <c r="F37">
-        <v>5.982857740082435</v>
+        <v>5.654618813457936</v>
       </c>
       <c r="G37">
-        <v>-6.599994416472692</v>
+        <v>-7.37982121509364</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>6.013622851747694</v>
       </c>
       <c r="E38">
-        <v>-17.32270240086011</v>
+        <v>-18.84261161729436</v>
       </c>
       <c r="F38">
-        <v>5.660579745288482</v>
+        <v>5.912347106756141</v>
       </c>
       <c r="G38">
-        <v>-6.772622070326285</v>
+        <v>-7.700015985470729</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.959590808860882</v>
       </c>
       <c r="E39">
-        <v>-18.09517478801027</v>
+        <v>-18.1005656563099</v>
       </c>
       <c r="F39">
-        <v>6.326978126553406</v>
+        <v>5.85176197165019</v>
       </c>
       <c r="G39">
-        <v>-6.518486970338136</v>
+        <v>-7.876399195418638</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.856921394935618</v>
       </c>
       <c r="E40">
-        <v>-16.51506477342263</v>
+        <v>-18.40505419137838</v>
       </c>
       <c r="F40">
-        <v>5.991348505961129</v>
+        <v>6.07240094285545</v>
       </c>
       <c r="G40">
-        <v>-7.565920311037377</v>
+        <v>-8.63352426444756</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.707308359756261</v>
       </c>
       <c r="E41">
-        <v>-15.93223216857546</v>
+        <v>-17.48591945271454</v>
       </c>
       <c r="F41">
-        <v>6.048078419174451</v>
+        <v>6.245768299852553</v>
       </c>
       <c r="G41">
-        <v>-7.449199141857885</v>
+        <v>-8.510519033037257</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.510706105520396</v>
       </c>
       <c r="E42">
-        <v>-14.95778911469889</v>
+        <v>-17.82395347565366</v>
       </c>
       <c r="F42">
-        <v>6.206700836401723</v>
+        <v>6.303682778451877</v>
       </c>
       <c r="G42">
-        <v>-7.497654561468947</v>
+        <v>-8.93212295556696</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.271136540512557</v>
       </c>
       <c r="E43">
-        <v>-15.32215449743742</v>
+        <v>-16.27980196471639</v>
       </c>
       <c r="F43">
-        <v>6.238011467492738</v>
+        <v>6.448779612726239</v>
       </c>
       <c r="G43">
-        <v>-7.882118031445472</v>
+        <v>-9.26678908321259</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.996669407499547</v>
       </c>
       <c r="E44">
-        <v>-14.03683111626346</v>
+        <v>-16.07390651328801</v>
       </c>
       <c r="F44">
-        <v>6.148582579421309</v>
+        <v>6.38182101882315</v>
       </c>
       <c r="G44">
-        <v>-8.022871104586162</v>
+        <v>-9.506749145443289</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.689056692257243</v>
       </c>
       <c r="E45">
-        <v>-12.5497738014086</v>
+        <v>-15.94810158904763</v>
       </c>
       <c r="F45">
-        <v>6.161563096623178</v>
+        <v>6.320448934684539</v>
       </c>
       <c r="G45">
-        <v>-7.451995249314967</v>
+        <v>-9.289345916479808</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.356904915730451</v>
       </c>
       <c r="E46">
-        <v>-13.63395715812112</v>
+        <v>-14.79353376001325</v>
       </c>
       <c r="F46">
-        <v>5.937271025171572</v>
+        <v>6.422540246875162</v>
       </c>
       <c r="G46">
-        <v>-7.904877197418502</v>
+        <v>-9.672966115953404</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.003306483862207</v>
       </c>
       <c r="E47">
-        <v>-12.52066394323288</v>
+        <v>-13.65080258325462</v>
       </c>
       <c r="F47">
-        <v>5.929582118938788</v>
+        <v>6.682216860304751</v>
       </c>
       <c r="G47">
-        <v>-8.644826177782489</v>
+        <v>-9.806786356832392</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>3.633492267339486</v>
       </c>
       <c r="E48">
-        <v>-11.02463984512771</v>
+        <v>-13.96154170136697</v>
       </c>
       <c r="F48">
-        <v>6.102261930991567</v>
+        <v>6.476823162780613</v>
       </c>
       <c r="G48">
-        <v>-8.291336581634933</v>
+        <v>-10.02284896844834</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>3.256416258829645</v>
       </c>
       <c r="E49">
-        <v>-11.65259293780781</v>
+        <v>-12.71656676821372</v>
       </c>
       <c r="F49">
-        <v>5.987349148140414</v>
+        <v>6.5887869576778</v>
       </c>
       <c r="G49">
-        <v>-8.599242577221652</v>
+        <v>-10.013634345414</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>2.876013882407343</v>
       </c>
       <c r="E50">
-        <v>-10.97481792207507</v>
+        <v>-13.02396255120957</v>
       </c>
       <c r="F50">
-        <v>6.15071314038131</v>
+        <v>6.557887196818573</v>
       </c>
       <c r="G50">
-        <v>-8.438371106261842</v>
+        <v>-10.16080071264276</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>2.504295958353917</v>
       </c>
       <c r="E51">
-        <v>-10.75748867986944</v>
+        <v>-12.20512371282903</v>
       </c>
       <c r="F51">
-        <v>5.67947811921595</v>
+        <v>6.401706806694754</v>
       </c>
       <c r="G51">
-        <v>-8.37077240193644</v>
+        <v>-10.02140000520027</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>2.14843571828844</v>
       </c>
       <c r="E52">
-        <v>-10.72881490888282</v>
+        <v>-12.06019325043781</v>
       </c>
       <c r="F52">
-        <v>5.435316827240795</v>
+        <v>6.546808611173533</v>
       </c>
       <c r="G52">
-        <v>-7.964898215568196</v>
+        <v>-10.53810943706734</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.816198760025469</v>
       </c>
       <c r="E53">
-        <v>-9.588613037821021</v>
+        <v>-11.56934181680163</v>
       </c>
       <c r="F53">
-        <v>5.90339576860149</v>
+        <v>6.119660959919967</v>
       </c>
       <c r="G53">
-        <v>-8.83244603245055</v>
+        <v>-11.0869323327774</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.515415310884112</v>
       </c>
       <c r="E54">
-        <v>-9.554602390282001</v>
+        <v>-11.20495566800647</v>
       </c>
       <c r="F54">
-        <v>5.803522824315564</v>
+        <v>6.741758252483174</v>
       </c>
       <c r="G54">
-        <v>-9.088275505678332</v>
+        <v>-10.41019078433656</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.246744085544075</v>
       </c>
       <c r="E55">
-        <v>-9.299723964488598</v>
+        <v>-10.57356371634941</v>
       </c>
       <c r="F55">
-        <v>5.575440143628748</v>
+        <v>6.5856209374643</v>
       </c>
       <c r="G55">
-        <v>-9.21420216028609</v>
+        <v>-11.01359129572385</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.013154671955047</v>
       </c>
       <c r="E56">
-        <v>-8.654692866840803</v>
+        <v>-10.2606898476161</v>
       </c>
       <c r="F56">
-        <v>5.228677265142847</v>
+        <v>6.15852795845932</v>
       </c>
       <c r="G56">
-        <v>-8.980449143320762</v>
+        <v>-11.02399902903632</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.8109830731963531</v>
       </c>
       <c r="E57">
-        <v>-8.759993386770505</v>
+        <v>-10.2825025134941</v>
       </c>
       <c r="F57">
-        <v>5.456238074365899</v>
+        <v>6.271457629748172</v>
       </c>
       <c r="G57">
-        <v>-8.801789364089402</v>
+        <v>-11.12864680985421</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.6353812997759024</v>
       </c>
       <c r="E58">
-        <v>-9.40237473559306</v>
+        <v>-9.610039455045813</v>
       </c>
       <c r="F58">
-        <v>5.804732240723651</v>
+        <v>6.166379224703054</v>
       </c>
       <c r="G58">
-        <v>-10.38373349865022</v>
+        <v>-11.52566273982481</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.481024699454561</v>
       </c>
       <c r="E59">
-        <v>-7.289960085136117</v>
+        <v>-9.438154651156458</v>
       </c>
       <c r="F59">
-        <v>5.488479790417662</v>
+        <v>6.515985060115363</v>
       </c>
       <c r="G59">
-        <v>-9.585718947835284</v>
+        <v>-11.54043694346592</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.3384852598940978</v>
       </c>
       <c r="E60">
-        <v>-7.494073808906141</v>
+        <v>-9.435363693146174</v>
       </c>
       <c r="F60">
-        <v>5.789337860910026</v>
+        <v>6.218201889422192</v>
       </c>
       <c r="G60">
-        <v>-9.946924599621877</v>
+        <v>-11.03884372278139</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.201794283068147</v>
       </c>
       <c r="E61">
-        <v>-7.089052640508862</v>
+        <v>-8.71434959431064</v>
       </c>
       <c r="F61">
-        <v>5.324295714447994</v>
+        <v>6.498339177700928</v>
       </c>
       <c r="G61">
-        <v>-10.01664192318296</v>
+        <v>-11.98007980574792</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.06440823043414258</v>
       </c>
       <c r="E62">
-        <v>-8.086217913543571</v>
+        <v>-8.672377240661922</v>
       </c>
       <c r="F62">
-        <v>4.940315945289117</v>
+        <v>6.230226470641229</v>
       </c>
       <c r="G62">
-        <v>-10.0002673331075</v>
+        <v>-11.91118095061614</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.078937617966798</v>
       </c>
       <c r="E63">
-        <v>-7.277824401644969</v>
+        <v>-8.26620978593899</v>
       </c>
       <c r="F63">
-        <v>5.433540807529193</v>
+        <v>6.564201013162711</v>
       </c>
       <c r="G63">
-        <v>-10.56278358419795</v>
+        <v>-12.13268957544915</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.229828933555121</v>
       </c>
       <c r="E64">
-        <v>-6.270350858102036</v>
+        <v>-8.51100421463571</v>
       </c>
       <c r="F64">
-        <v>5.537038687569769</v>
+        <v>6.234976329328881</v>
       </c>
       <c r="G64">
-        <v>-10.33221437026149</v>
+        <v>-12.19873358137054</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.390365524292949</v>
       </c>
       <c r="E65">
-        <v>-6.830768581429099</v>
+        <v>-7.836431324834408</v>
       </c>
       <c r="F65">
-        <v>5.495711437844101</v>
+        <v>6.282274451293928</v>
       </c>
       <c r="G65">
-        <v>-9.959701583650785</v>
+        <v>-12.22541539109172</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.5595517850167648</v>
       </c>
       <c r="E66">
-        <v>-8.050101587862862</v>
+        <v>-8.209119743067896</v>
       </c>
       <c r="F66">
-        <v>5.042844635468417</v>
+        <v>6.021227718180108</v>
       </c>
       <c r="G66">
-        <v>-10.5031045735897</v>
+        <v>-12.27894087669872</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.7358121278731817</v>
       </c>
       <c r="E67">
-        <v>-6.0544087884789</v>
+        <v>-7.699778212613574</v>
       </c>
       <c r="F67">
-        <v>5.479127522440056</v>
+        <v>6.218133963295162</v>
       </c>
       <c r="G67">
-        <v>-11.32291492562354</v>
+        <v>-12.20451115915068</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.9187342432193843</v>
       </c>
       <c r="E68">
-        <v>-7.191288090480842</v>
+        <v>-8.339318764889947</v>
       </c>
       <c r="F68">
-        <v>5.297459924066901</v>
+        <v>6.279380135588545</v>
       </c>
       <c r="G68">
-        <v>-10.73148467818651</v>
+        <v>-12.40005853976965</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.105193529797541</v>
       </c>
       <c r="E69">
-        <v>-6.408075498844675</v>
+        <v>-7.968557436711178</v>
       </c>
       <c r="F69">
-        <v>5.291223974258627</v>
+        <v>6.38485118678259</v>
       </c>
       <c r="G69">
-        <v>-11.38110581181487</v>
+        <v>-12.33884832745871</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.294523524435507</v>
       </c>
       <c r="E70">
-        <v>-5.581432776384776</v>
+        <v>-7.316299751358181</v>
       </c>
       <c r="F70">
-        <v>5.52055748972367</v>
+        <v>6.437581742175196</v>
       </c>
       <c r="G70">
-        <v>-9.930940315862784</v>
+        <v>-11.60676943666463</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.484951553500685</v>
       </c>
       <c r="E71">
-        <v>-6.853320518922919</v>
+        <v>-7.921775664348309</v>
       </c>
       <c r="F71">
-        <v>5.152257058764982</v>
+        <v>6.034572717039208</v>
       </c>
       <c r="G71">
-        <v>-10.54993480469279</v>
+        <v>-12.19009071140166</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.674997222588326</v>
       </c>
       <c r="E72">
-        <v>-6.936758534438725</v>
+        <v>-7.468485873933873</v>
       </c>
       <c r="F72">
-        <v>5.424282973435505</v>
+        <v>6.44917060214036</v>
       </c>
       <c r="G72">
-        <v>-10.84644620551159</v>
+        <v>-12.00950681340665</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.865138197205231</v>
       </c>
       <c r="E73">
-        <v>-7.885576274441104</v>
+        <v>-7.724145103456343</v>
       </c>
       <c r="F73">
-        <v>5.516240038820279</v>
+        <v>6.256720973652368</v>
       </c>
       <c r="G73">
-        <v>-9.753738637485561</v>
+        <v>-11.79736292942197</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.051855009790041</v>
       </c>
       <c r="E74">
-        <v>-7.132063296988786</v>
+        <v>-7.698939263925959</v>
       </c>
       <c r="F74">
-        <v>5.231939375975072</v>
+        <v>6.40169355281631</v>
       </c>
       <c r="G74">
-        <v>-10.04402993931604</v>
+        <v>-11.85190399467492</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.23254252686636</v>
       </c>
       <c r="E75">
-        <v>-6.733998757560594</v>
+        <v>-8.031594878199426</v>
       </c>
       <c r="F75">
-        <v>5.428497706780949</v>
+        <v>5.980745403205296</v>
       </c>
       <c r="G75">
-        <v>-10.20269663646865</v>
+        <v>-11.73425209504869</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.402108792047532</v>
       </c>
       <c r="E76">
-        <v>-6.931596092761962</v>
+        <v>-8.574502662581013</v>
       </c>
       <c r="F76">
-        <v>5.448290717503441</v>
+        <v>6.326225968951664</v>
       </c>
       <c r="G76">
-        <v>-11.30300277662712</v>
+        <v>-11.34240935548539</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.554937458428705</v>
       </c>
       <c r="E77">
-        <v>-7.441112058091928</v>
+        <v>-8.462947406396118</v>
       </c>
       <c r="F77">
-        <v>5.27805458928892</v>
+        <v>6.472492457998777</v>
       </c>
       <c r="G77">
-        <v>-9.835961427638084</v>
+        <v>-11.08134925546931</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.687897783256862</v>
       </c>
       <c r="E78">
-        <v>-7.817226875668401</v>
+        <v>-9.350467900455353</v>
       </c>
       <c r="F78">
-        <v>5.453857346450254</v>
+        <v>6.582524500112636</v>
       </c>
       <c r="G78">
-        <v>-9.708835135890709</v>
+        <v>-11.03774329393624</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.795975240275039</v>
       </c>
       <c r="E79">
-        <v>-8.146622219051878</v>
+        <v>-9.016188380553878</v>
       </c>
       <c r="F79">
-        <v>4.851312838062727</v>
+        <v>6.324824371306127</v>
       </c>
       <c r="G79">
-        <v>-9.877486625732036</v>
+        <v>-10.82407473511034</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.876524263948301</v>
       </c>
       <c r="E80">
-        <v>-9.205495905950889</v>
+        <v>-10.20336722491082</v>
       </c>
       <c r="F80">
-        <v>5.143540976952726</v>
+        <v>6.274653471188172</v>
       </c>
       <c r="G80">
-        <v>-8.682029288205854</v>
+        <v>-10.74649384884082</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.925991910073461</v>
       </c>
       <c r="E81">
-        <v>-8.370559220475307</v>
+        <v>-10.85139278792382</v>
       </c>
       <c r="F81">
-        <v>4.946092979556241</v>
+        <v>6.466230000433614</v>
       </c>
       <c r="G81">
-        <v>-9.440267839802885</v>
+        <v>-10.51987208072612</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.939324648982789</v>
       </c>
       <c r="E82">
-        <v>-10.44663742505132</v>
+        <v>-11.11381759869443</v>
       </c>
       <c r="F82">
-        <v>5.281343207878034</v>
+        <v>6.475557417389136</v>
       </c>
       <c r="G82">
-        <v>-8.903229845177108</v>
+        <v>-10.18218662696087</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.913411720542017</v>
       </c>
       <c r="E83">
-        <v>-11.67328423662811</v>
+        <v>-11.9127376355611</v>
       </c>
       <c r="F83">
-        <v>5.662715276452898</v>
+        <v>6.395061643389496</v>
       </c>
       <c r="G83">
-        <v>-9.069962437743968</v>
+        <v>-10.13508096230341</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.843572008980391</v>
       </c>
       <c r="E84">
-        <v>-12.81537997205404</v>
+        <v>-12.7828063356334</v>
       </c>
       <c r="F84">
-        <v>5.706448105116296</v>
+        <v>6.739962351953904</v>
       </c>
       <c r="G84">
-        <v>-9.498189819301325</v>
+        <v>-10.04049890725656</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.726350542261952</v>
       </c>
       <c r="E85">
-        <v>-13.64386672034216</v>
+        <v>-14.34784849953457</v>
       </c>
       <c r="F85">
-        <v>5.32208728695213</v>
+        <v>6.473223078048047</v>
       </c>
       <c r="G85">
-        <v>-9.022877659043239</v>
+        <v>-9.951002582673196</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.560378226054561</v>
       </c>
       <c r="E86">
-        <v>-16.54741413643172</v>
+        <v>-14.49785833937605</v>
       </c>
       <c r="F86">
-        <v>4.970253143226291</v>
+        <v>6.454495347805556</v>
       </c>
       <c r="G86">
-        <v>-9.152279214701769</v>
+        <v>-10.31262725896666</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.343979821407882</v>
       </c>
       <c r="E87">
-        <v>-14.70016126300845</v>
+        <v>-15.90956809437587</v>
       </c>
       <c r="F87">
-        <v>5.418181219146485</v>
+        <v>6.323694478168708</v>
       </c>
       <c r="G87">
-        <v>-9.292776434872531</v>
+        <v>-9.472052349827393</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.080673600355381</v>
       </c>
       <c r="E88">
-        <v>-17.87433192902384</v>
+        <v>-18.57518634008865</v>
       </c>
       <c r="F88">
-        <v>5.274615207832497</v>
+        <v>6.513526465663854</v>
       </c>
       <c r="G88">
-        <v>-8.12409097775592</v>
+        <v>-9.554515328482298</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.775750239946322</v>
       </c>
       <c r="E89">
-        <v>-18.41464810953873</v>
+        <v>-18.78144312090228</v>
       </c>
       <c r="F89">
-        <v>5.224172603206424</v>
+        <v>6.464069618247112</v>
       </c>
       <c r="G89">
-        <v>-8.122846957958254</v>
+        <v>-8.930556508812291</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.436431775843779</v>
       </c>
       <c r="E90">
-        <v>-20.30948432511055</v>
+        <v>-20.32799103477399</v>
       </c>
       <c r="F90">
-        <v>5.18866380611802</v>
+        <v>6.633921383986734</v>
       </c>
       <c r="G90">
-        <v>-7.644310528130145</v>
+        <v>-8.897436602929428</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.074609715343462</v>
       </c>
       <c r="E91">
-        <v>-22.23686095141241</v>
+        <v>-22.28921218016188</v>
       </c>
       <c r="F91">
-        <v>5.441193265596254</v>
+        <v>6.701943601635018</v>
       </c>
       <c r="G91">
-        <v>-7.750822380586089</v>
+        <v>-8.582310593175986</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.700964920831592</v>
       </c>
       <c r="E92">
-        <v>-23.85896823891672</v>
+        <v>-23.74312271543328</v>
       </c>
       <c r="F92">
-        <v>4.899702748264663</v>
+        <v>6.374117201977114</v>
       </c>
       <c r="G92">
-        <v>-8.344431294384403</v>
+        <v>-8.551720498801911</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.3296760764861775</v>
       </c>
       <c r="E93">
-        <v>-25.90371461725823</v>
+        <v>-26.62107804333924</v>
       </c>
       <c r="F93">
-        <v>5.240814504328665</v>
+        <v>6.341075283014248</v>
       </c>
       <c r="G93">
-        <v>-7.621057931429394</v>
+        <v>-8.485137374122454</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.02744815600421304</v>
       </c>
       <c r="E94">
-        <v>-28.48389092299097</v>
+        <v>-28.67232004419278</v>
       </c>
       <c r="F94">
-        <v>5.2963350011339</v>
+        <v>6.485598887045872</v>
       </c>
       <c r="G94">
-        <v>-7.957716057198044</v>
+        <v>-8.226459578545768</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.3630819882923003</v>
       </c>
       <c r="E95">
-        <v>-31.3275822574671</v>
+        <v>-30.20150753472671</v>
       </c>
       <c r="F95">
-        <v>4.597393378082595</v>
+        <v>6.061347208232494</v>
       </c>
       <c r="G95">
-        <v>-6.877098847373457</v>
+        <v>-7.934429520817608</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.6720569406478677</v>
       </c>
       <c r="E96">
-        <v>-33.07001015365736</v>
+        <v>-32.56926577064543</v>
       </c>
       <c r="F96">
-        <v>4.231079372155819</v>
+        <v>5.727778565738383</v>
       </c>
       <c r="G96">
-        <v>-7.017901524661379</v>
+        <v>-7.9447732908876</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.9553137993797824</v>
       </c>
       <c r="E97">
-        <v>-35.93192577942683</v>
+        <v>-35.15137124303855</v>
       </c>
       <c r="F97">
-        <v>5.199480627663776</v>
+        <v>5.468820975214424</v>
       </c>
       <c r="G97">
-        <v>-7.123600130177191</v>
+        <v>-7.704969873332367</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.217250896159489</v>
       </c>
       <c r="E98">
-        <v>-38.37658902944741</v>
+        <v>-37.5178523664749</v>
       </c>
       <c r="F98">
-        <v>4.600902342400853</v>
+        <v>5.514265210932005</v>
       </c>
       <c r="G98">
-        <v>-7.261343014804328</v>
+        <v>-7.869476806135301</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.460916951834942</v>
       </c>
       <c r="E99">
-        <v>-41.0322727936712</v>
+        <v>-40.40809081687404</v>
       </c>
       <c r="F99">
-        <v>4.076782689505967</v>
+        <v>5.081050596820337</v>
       </c>
       <c r="G99">
-        <v>-7.430950037166003</v>
+        <v>-7.448731818576075</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.699007052853131</v>
       </c>
       <c r="E100">
-        <v>-43.80517887093261</v>
+        <v>-42.52457353782366</v>
       </c>
       <c r="F100">
-        <v>4.079812857465408</v>
+        <v>5.162283617808467</v>
       </c>
       <c r="G100">
-        <v>-6.280666413299853</v>
+        <v>-7.216106643274109</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.928259484776009</v>
       </c>
       <c r="E101">
-        <v>-45.16337242140635</v>
+        <v>-45.01592095974097</v>
       </c>
       <c r="F101">
-        <v>3.679047051256201</v>
+        <v>4.677332489187553</v>
       </c>
       <c r="G101">
-        <v>-6.989373918514284</v>
+        <v>-7.251325587808227</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>2.164448838118794</v>
       </c>
       <c r="E102">
-        <v>-48.05728438722231</v>
+        <v>-47.41784974183472</v>
       </c>
       <c r="F102">
-        <v>3.624043455710314</v>
+        <v>3.953263169339727</v>
       </c>
       <c r="G102">
-        <v>-6.895810053857966</v>
+        <v>-7.387924966304456</v>
       </c>
     </row>
   </sheetData>
